--- a/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuKhongMa.xlsx
@@ -314,6 +314,622 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K26TVA</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1955142</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0100109106-122</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Viettel Thành Phố Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Tnhh Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>64000.0</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>864000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K26TVA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1955463</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100109106-122</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Viettel Thành Phố Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Tnhh Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K26TDA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1219348</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="13" t="n">
+        <v>110320.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>8826.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>119146.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K26TDA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1356709</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="13" t="n">
+        <v>4025104.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>322008.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>4347112.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K26TDA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>1356712</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="13" t="n">
+        <v>567360.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>45389.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>612749.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K26THE</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>639981</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="13" t="n">
+        <v>163453.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>16345.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>179798.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K26THE</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>639983</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="13" t="n">
+        <v>191818.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>19182.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>211000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K26THE</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>639984</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="13" t="n">
+        <v>163636.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>16364.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>180000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
